--- a/docs/modules/bsee/analysis/production/project_economics_V30/lease_assumptions.xlsx
+++ b/docs/modules/bsee/analysis/production/project_economics_V30/lease_assumptions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07f9c9cfd5dcd705/Roy/FDAS/Mktg/1-World Oil/2025 article/WAR/eWellWARRawData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="13" documentId="11_C42A9AB4844DBA0E62355476585DCE3AE7CD9151" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB8D768-8CAB-4967-8FB9-9A02FEE07700}"/>
